--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD518FD-A03A-48AA-B3FE-13F481BFD7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861517F7-C7A3-4F9B-8A82-016C797B8DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>Felt unwell due to health issues.</t>
+  </si>
+  <si>
+    <t>18-08-2026</t>
+  </si>
+  <si>
+    <t>Feeling some better than yesterday</t>
   </si>
 </sst>
 </file>
@@ -1275,27 +1281,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>180</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>400</v>
+      </c>
+      <c r="G12" s="14">
+        <v>8</v>
+      </c>
+      <c r="H12" s="14">
+        <v>200</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861517F7-C7A3-4F9B-8A82-016C797B8DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E6C911-031F-4051-8661-F1C421C2050D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,15 @@
   </si>
   <si>
     <t>Feeling some better than yesterday</t>
+  </si>
+  <si>
+    <t>19-08-2026</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>It's a nice experience.</t>
   </si>
 </sst>
 </file>
@@ -1077,11 +1086,11 @@
         <v>120</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f t="shared" ref="I7:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>1240</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" ref="J6:J69" si="1">IF(I7="","",1440-I7)</f>
+        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
         <v>200</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1328,26 +1337,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="14">
+        <v>480</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>70</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="14">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>180</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E6C911-031F-4051-8661-F1C421C2050D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88B356B-4201-4773-93B7-0073A41DE150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,18 @@
   </si>
   <si>
     <t>It's a nice experience.</t>
+  </si>
+  <si>
+    <t>20-08-2026</t>
+  </si>
+  <si>
+    <t>Better</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>It's a nice day.</t>
   </si>
 </sst>
 </file>
@@ -1383,26 +1395,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="14">
+        <v>480</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>200</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>200</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88B356B-4201-4773-93B7-0073A41DE150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70AD5A9-C469-4B45-9E54-CC70AAD10819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,27 @@
   </si>
   <si>
     <t>It's a nice day.</t>
+  </si>
+  <si>
+    <t>21-08-2026</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Today I met a PHD scholar and it’s a very nice experience to met her.</t>
+  </si>
+  <si>
+    <t>22-08-2026</t>
+  </si>
+  <si>
+    <t>Unwell</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Feeling unhealthy.</t>
   </si>
 </sst>
 </file>
@@ -1440,49 +1461,97 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>180</v>
+      </c>
+      <c r="E15" s="14">
+        <v>80</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>200</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>250</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70AD5A9-C469-4B45-9E54-CC70AAD10819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB82757-D678-4A5C-AA00-4D0FA58DEA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,9 +283,6 @@
     <t>21-08-2026</t>
   </si>
   <si>
-    <t>medium</t>
-  </si>
-  <si>
     <t>Today I met a PHD scholar and it’s a very nice experience to met her.</t>
   </si>
   <si>
@@ -299,6 +296,12 @@
   </si>
   <si>
     <t>Feeling unhealthy.</t>
+  </si>
+  <si>
+    <t>23-08-2026</t>
+  </si>
+  <si>
+    <t>I am switzerland.</t>
   </si>
 </sst>
 </file>
@@ -1504,12 +1507,12 @@
         <v>49</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="14">
         <v>480</v>
@@ -1541,39 +1544,63 @@
         <v>380</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="M16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="N16" s="17" t="s">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>240</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB82757-D678-4A5C-AA00-4D0FA58DEA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4A9614-1E79-4526-91CB-A1C9160312F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>I am switzerland.</t>
+  </si>
+  <si>
+    <t>24-08-2026</t>
+  </si>
+  <si>
+    <t>As usual attended the classes and spend some time in library also.</t>
   </si>
 </sst>
 </file>
@@ -1602,27 +1608,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>90</v>
+      </c>
+      <c r="F18" s="14">
+        <v>150</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>230</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4A9614-1E79-4526-91CB-A1C9160312F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE43D0A-37E0-44B2-9607-CFFC1498A298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>As usual attended the classes and spend some time in library also.</t>
+  </si>
+  <si>
+    <t>25-08-2026</t>
+  </si>
+  <si>
+    <t>Today I got late for first class due to some health issues.</t>
   </si>
 </sst>
 </file>
@@ -1654,27 +1660,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>180</v>
+      </c>
+      <c r="E19" s="14">
+        <v>70</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>200</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE43D0A-37E0-44B2-9607-CFFC1498A298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4367641C-04C9-4A2A-83EF-CE21EF8453A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t>Today I got late for first class due to some health issues.</t>
+  </si>
+  <si>
+    <t>26-08-2026</t>
+  </si>
+  <si>
+    <t>I learned a lesson after yesterday and today I arrived 5 minutes early.</t>
   </si>
 </sst>
 </file>
@@ -1706,27 +1712,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="20" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="14">
+        <v>480</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>180</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>240</v>
+      </c>
+      <c r="G20" s="14">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4367641C-04C9-4A2A-83EF-CE21EF8453A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB37948-3EBA-45FC-80E2-A924FF3166CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,18 @@
   </si>
   <si>
     <t>I learned a lesson after yesterday and today I arrived 5 minutes early.</t>
+  </si>
+  <si>
+    <t>27-08-2026</t>
+  </si>
+  <si>
+    <t>Outstanding</t>
+  </si>
+  <si>
+    <t>Very High</t>
+  </si>
+  <si>
+    <t>Today I attended an event in unipolis and I enjoyed it very much.</t>
   </si>
 </sst>
 </file>
@@ -1758,27 +1770,51 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>360</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>200</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB37948-3EBA-45FC-80E2-A924FF3166CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A2E814-06D6-46CF-9B95-915CFEABCEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>Today I attended an event in unipolis and I enjoyed it very much.</t>
+  </si>
+  <si>
+    <t>28-08-2026</t>
+  </si>
+  <si>
+    <t>Very nice</t>
   </si>
 </sst>
 </file>
@@ -1817,26 +1823,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="14">
+        <v>480</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>120</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
+        <v>250</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A2E814-06D6-46CF-9B95-915CFEABCEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F00ACC3-0C34-4B72-9E25-1AC5707BF2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>Very nice</t>
+  </si>
+  <si>
+    <t>29-08-2026</t>
+  </si>
+  <si>
+    <t>Today was my mentor meeting and it's a nice experience.</t>
   </si>
 </sst>
 </file>
@@ -1868,27 +1874,51 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>220</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>30</v>
+      </c>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>250</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F00ACC3-0C34-4B72-9E25-1AC5707BF2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ECAAD0-430E-4A00-A808-BEE580918221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>Today was my mentor meeting and it's a nice experience.</t>
+  </si>
+  <si>
+    <t>30-08-2026</t>
+  </si>
+  <si>
+    <t>Today I gave my first mars test.</t>
   </si>
 </sst>
 </file>
@@ -1921,26 +1927,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>200</v>
+      </c>
+      <c r="E24" s="14">
+        <v>100</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>200</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ECAAD0-430E-4A00-A808-BEE580918221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7B1135-163B-4658-8354-B896FC5778B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Today I gave my first mars test.</t>
+  </si>
+  <si>
+    <t>31-08-2026</t>
   </si>
 </sst>
 </file>
@@ -1973,25 +1976,47 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>250</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
+      <c r="F25" s="14">
+        <v>100</v>
+      </c>
+      <c r="G25" s="14">
+        <v>2</v>
+      </c>
+      <c r="H25" s="14">
+        <v>200</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7B1135-163B-4658-8354-B896FC5778B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507B2A9E-6068-4C2F-865D-28B373362517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,12 @@
   </si>
   <si>
     <t>31-08-2026</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>It's a new day of new month also begenning of a new journey.</t>
   </si>
 </sst>
 </file>
@@ -2019,27 +2025,51 @@
       </c>
       <c r="N25" s="17"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46031</v>
+      </c>
+      <c r="B26" s="14">
+        <v>480</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>200</v>
+      </c>
+      <c r="E26" s="14">
+        <v>90</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>180</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507B2A9E-6068-4C2F-865D-28B373362517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCF6531-56FD-407C-A9A5-429EC8B43796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2072,25 +2072,47 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46062</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>220</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>210</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCF6531-56FD-407C-A9A5-429EC8B43796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E2DD0A-2F9F-42AD-A399-708C39DCAEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>It's a new day of new month also begenning of a new journey.</t>
+  </si>
+  <si>
+    <t>Today i joined punjabi dance club because dance give me energy even after tired .</t>
   </si>
 </sst>
 </file>
@@ -2115,27 +2118,51 @@
       </c>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46090</v>
+      </c>
+      <c r="B28" s="14">
+        <v>480</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>200</v>
+      </c>
+      <c r="E28" s="14">
+        <v>90</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>200</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E2DD0A-2F9F-42AD-A399-708C39DCAEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1463F37C-DB53-464D-B357-D61EF2E38F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,15 @@
   </si>
   <si>
     <t>Today i joined punjabi dance club because dance give me energy even after tired .</t>
+  </si>
+  <si>
+    <t>Very good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I regestered for heckathon </t>
+  </si>
+  <si>
+    <t>Preparing for heckathon as well as for CA.</t>
   </si>
 </sst>
 </file>
@@ -2164,49 +2173,97 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46121</v>
+      </c>
+      <c r="B29" s="14">
+        <v>480</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>200</v>
+      </c>
+      <c r="E29" s="14">
+        <v>90</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>220</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>90</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46151</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>220</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>200</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1463F37C-DB53-464D-B357-D61EF2E38F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82038A96-8EB8-4B8C-8F8A-82723F2A711C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>Preparing for heckathon as well as for CA.</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -2266,47 +2269,91 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46182</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>210</v>
+      </c>
+      <c r="E31" s="14">
+        <v>90</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>180</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46212</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>220</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>220</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82038A96-8EB8-4B8C-8F8A-82723F2A711C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA48507-28A3-40B6-AC5C-82FF8F582E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>My CA is going on and datesheet of Mid Term exam is already came.</t>
   </si>
 </sst>
 </file>
@@ -2356,27 +2359,51 @@
       </c>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46243</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>240</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA48507-28A3-40B6-AC5C-82FF8F582E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAE3E25-4C3E-44F4-BB25-69A558FDD0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2406,25 +2406,47 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>200</v>
+      </c>
+      <c r="E34" s="14">
+        <v>90</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAE3E25-4C3E-44F4-BB25-69A558FDD0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9FBE7B-6568-4CF9-9662-3C46CEE3433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>My CA is going on and datesheet of Mid Term exam is already came.</t>
+  </si>
+  <si>
+    <t>Today is freshers party and I participated in modeling and its  very great experience.</t>
   </si>
 </sst>
 </file>
@@ -2449,27 +2452,51 @@
       </c>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <v>46335</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>220</v>
+      </c>
+      <c r="E35" s="14">
+        <v>90</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9FBE7B-6568-4CF9-9662-3C46CEE3433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B36CE-C4DA-4F3C-BDBA-9C05CBFB962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>Today is freshers party and I participated in modeling and its  very great experience.</t>
+  </si>
+  <si>
+    <t>Today is my dbms CA and it was very good.</t>
   </si>
 </sst>
 </file>
@@ -2498,27 +2501,51 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>46365</v>
+      </c>
+      <c r="B36" s="14">
+        <v>480</v>
+      </c>
+      <c r="C36" s="14">
+        <v>70</v>
+      </c>
+      <c r="D36" s="14">
+        <v>200</v>
+      </c>
+      <c r="E36" s="14">
+        <v>100</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>180</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4B36CE-C4DA-4F3C-BDBA-9C05CBFB962B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07E9A63-810A-4C20-BB97-E91A2938B7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>Today is my dbms CA and it was very good.</t>
+  </si>
+  <si>
+    <t>13-09-2026</t>
   </si>
 </sst>
 </file>
@@ -2548,25 +2551,47 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>240</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
